--- a/release_notes/ANLYMD/ANLYMD_14.0_vs_13.6.xlsx
+++ b/release_notes/ANLYMD/ANLYMD_14.0_vs_13.6.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Readme" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="New Terms" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Term Name Changes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Existing Terms Changes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -463,14 +463,10 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Term Name Changes Spreadsheet</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
+          <t>New Terms Spreadsheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -487,36 +483,36 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Change</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Either a Scope Note change or a Name change</t>
+          <t>The commonly accepted name of the term added to the catalogue</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Old Value</t>
+          <t>Scope Note</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>The value of the term in the previous version</t>
+          <t>A brief desciption of the added term</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>New Value</t>
+          <t>masterParentCode</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>The value of the term in the current version</t>
+          <t>The term code of the parent term</t>
         </is>
       </c>
     </row>
@@ -527,7 +523,7 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>New Terms Spreadsheet</t>
+          <t>Existing Terms Changes Spreadsheet</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr"/>
@@ -547,106 +543,142 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Change</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>The commonly accepted name of the term added to the catalogue</t>
+          <t>Either a Scope Note change or a Name change</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Scope Note</t>
+          <t>Old Value</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A brief desciption of the added term</t>
+          <t>The value of the term in the previous version</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>masterParentCode</t>
+          <t>New Value</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>The term code of the parent term</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>masterReportable</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Indicates whether the term is reportable (1) in the hierarchy or not (0).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="10" customHeight="1">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>{hierarchy_name} Reportability Spreadsheets</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr"/>
+          <t>The value of the term in the current version</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="10" customHeight="1">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Deprecated Terms Spreadsheet</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>The uniquely identifying term code for the catalogue</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>The uniquely identifying term code for the catalogue</t>
+          <t>The commonly accepted name of the term in the catalogue</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>Scope Note</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>A brief desciption of the term</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="10" customHeight="1">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>{hierarchy_name} Reportability Spreadsheets</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>The uniquely identifying term code for the catalogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>The common name of added or changed term</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Reportability Old</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>The previous reportability value of the term, can be either empty, 0 or 1. Empty indicates that the term is newly added to the hierarchy. Whereas the value 0 indicates that the term is not reportable and the value 1 indicates that the term is reportable within the hierarchy</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Reportability New</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>The new reportability value of the term, indicates that the term is either not reportable (0) or reportable (1) within the given hierarchy</t>
         </is>
@@ -663,14 +695,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="66" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,11 +725,6 @@
           <t>masterParentCode</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>masterReportable</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -720,9 +746,6 @@
         <is>
           <t>F027A</t>
         </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -740,7 +763,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="47" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
   </cols>
@@ -775,7 +798,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Scope Note</t>
+          <t>ScopeNote</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
